--- a/log.xlsx
+++ b/log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,6 +598,125 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-07-10 16:21:21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>xuan_3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-07-10 16:23:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>xuan_3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-07-15 10:37:53</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>xuan_3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-07-15 11:57:59</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>xuan_3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-07-15 11:59:30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>xuan_3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-07-15 12:01:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>xuan_3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-07-31 16:29:42</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>xuan_3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
